--- a/reference/paper_summary_en.xlsx
+++ b/reference/paper_summary_en.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,11 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +54,13 @@
         <fgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -74,11 +82,17 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -87,6 +101,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -454,1739 +478,3217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Abb.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Codes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Motivation</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Key methods</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Eval-Data</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Eval-Comparison Models</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Eval-Experiments</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Metrics</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Key findings</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Limitations</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>PDF Link</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>IMMAX</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Balancing Scales: Theoretical Framework for Imbalanced Classification</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Standard loss functions lack theoretical guarantees under class imbalance</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Derive H-consistency bounds for imbalanced margin losses; propose IMMAX algorithm</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Class-imbalanced margin loss; H-consistency bounds analysis; IMMAX algorithm</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>CIFAR-10/100, standard classification benchmarks</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>CE loss, cost-sensitive variants, re-weighting baselines</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Imbalanced multi-class classification under varying IR</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Accuracy, balanced accuracy, F1</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>IMMAX achieves tighter theoretical bounds and competitive empirical performance over CE-based methods</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>Framework assumes standard classification; applicability to regression/detection unclear</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>ICML 2025</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O2" s="6" t="n"/>
     </row>
     <row r="3" ht="72" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>LSR</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Latent Score-based Reweighting for Long-tailed Tabular Data</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>github.com/YunzeTong/latent-score-based-reweighting</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>SMOTE introduces noise; density of minority regions in tabular data not exploited</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Reweight training samples by estimated density in VAE latent space to upweight underrepresented regions</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>VAE encoder; diffusion model for latent density estimation; density-based sample reweighting</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Multiple tabular classification benchmarks</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>SMOTE, ADASYN, class-reweighting, ROS/RUS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Binary/multiclass tabular imbalanced classification</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>AUC, balanced accuracy, F1</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>Outperforms SMOTE on low-density minority regions; VAE latent space better captures inter-class structure</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>Requires training VAE + diffusion model; computationally expensive for large tabular data</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>ICML 2025</t>
         </is>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O3" s="7" t="n"/>
     </row>
     <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>PRIME</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>PRIME: Proxy-based Representation for Imbalanced Regression</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Imbalanced regression underexplored; ordinal structure of target ignored</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Learn better representations for deep imbalanced regression (DIR) via proxy and alignment losses</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Ordinal-aware proxy loss; alignment loss between proxies and features; applicable to DIR tasks</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Age estimation (IMDB-WIKI), depth estimation (NYU-v2), stem cell count (SCI)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>DIR, RankSim, ConR, FDS, LDS</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Deep imbalanced regression tasks with varying label density</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>MAE, RMSE, geometric mean (GM)</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>PRIME improves tail-range performance while maintaining head accuracy; proxy loss captures ordinal proximity</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Assumes ordinal/continuous target structure; proxy design requires domain knowledge</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>ICML 2025</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O4" s="6" t="n"/>
     </row>
     <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>DP</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Differential Privacy under Class Imbalance</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>DP mechanisms further degrade tail-class performance in imbalanced settings</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Evaluate DP variants under class imbalance; identify which DP approaches preserve minority-class utility</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>DP pre-processing (DP-SMOTE); DP in-processing (DP-SGD variants); private synthetic data generation</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Standard classification benchmarks at varying IR</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>DP-SGD, standard SMOTE+DP, non-private baselines</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Binary/multiclass DP learning experiments with varying ε and IR</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Accuracy, recall, F1 per class; privacy budget ε</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Private synthetic data generation outperforms DP-SMOTE; in-processing DP-SGD insufficient alone for tail classes</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Privacy-utility tradeoff remains; synthetic data quality degrades at low ε</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>ICML 2025</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O5" s="7" t="n"/>
     </row>
     <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>DIRECT: Active Learning under Imbalance and Label Noise</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Active learning ignores simultaneous class imbalance and label noise; annotation cost high</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Reduce annotation budget while handling imbalance + noise via optimal separation threshold</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Optimal separation threshold; dual-criteria sample selection; noise-aware query strategy</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Standard imbalanced classification benchmarks with synthetic noise</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>BADGE, CoreSet, VAAL, CLUE, random sampling</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Active learning under varying IR and noise rates with fixed annotation budgets</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Balanced accuracy, annotation cost reduction (%)</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>DIRECT reduces annotation cost 60%+ vs SOTA; threshold approach robust to noise and imbalance simultaneously</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>Threshold tuning required; assumes some knowledge of noise model</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>ICML 2025</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O6" s="6" t="n"/>
     </row>
     <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>DCE</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Dual-Balance Collaborative Experts for Domain-Incremental Learning</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>github.com/Lain810/DCE</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Domain-incremental learning and intra-domain class imbalance compound each other; no method addresses both</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Jointly tackle cross-domain shift and intra-domain class imbalance in domain-incremental learning</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>3 frequency-aware experts (head/balanced/tail); DES router via Gaussian pseudo-sampling from class centroids/covariances; affinity matrix for expert collaboration</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Office-Home, DomainNet, CORe50, CDDB-Hard</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>EWC, DER, FOSTER, iCaRL, BEEF, CoRe, GKEAL</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Domain-incremental learning on multi-domain benchmarks with natural/synthetic imbalance</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Overall accuracy, balanced accuracy, per-domain accuracy</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>Outperforms SOTA on all 4 benchmarks; DES effectively routes rare-class samples to tail expert</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>Gaussian pseudo-sampling assumes unimodal class distributions; head/tail threshold is a hyperparameter</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>ICML 2025</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O7" s="7" t="n"/>
     </row>
     <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>IP2SL</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>IP2SL: Informative and Positive-Balanced Sampling for Long-tail Learning</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Random oversampling creates redundant/uninformative samples; MI not maximized in existing samplers</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Two-stage sampling maximizing mutual information and ensuring positive balance for long-tail</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>BNS (Balanced Negative Sampling via MI maximization); IP-DPP (informative subset via Determinantal Point Processes)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>SMOTE, MixUp, BalancedSoftmax, LDAM, RIDE</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Long-tail image classification; ablation on BNS vs IP-DPP contribution</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Accuracy (many/medium/few), balanced accuracy</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>IP2SL significantly outperforms random oversampling; BNS+IP-DPP synergistic; tail classes most improved</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>DPP computation O(n³) expensive for large datasets; MI estimation requires large memory</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>NeurIPS 2025</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O8" s="6" t="n"/>
     </row>
     <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>MORE</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>MORE: Model Rebalancing for Multi-label Long-tail Recognition</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Multi-label LT underexplored; existing single-label rebalancing fails for multi-label co-occurrence</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Plug-and-play rebalancing for multi-label long-tail classification via low-rank parameter decomposition</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Low-rank decomposition θ = θ^g ⊕ θ^t (global + tail-specific); sinusoidal reweighting schedule</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>COCO-LT, VOC-LT, nuImages</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>ASL, BCE, ResLT, DisAlign, OLTR</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Multi-label LT classification; plug-in ablations with existing methods</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>mAP (head/medium/tail/overall)</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>MORE improves tail mAP significantly; compatible with any multi-label classifier; minimal overhead</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Low-rank approximation may reduce capacity; sinusoidal schedule hyperparameter-sensitive</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>NeurIPS 2025</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O9" s="7" t="n"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>ImOOD</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ImOOD: Towards Balanced OOD Detection under Long-tailed Training Data</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>github.com/alibaba/imood</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>OOD detection methods biased toward head classes under imbalanced training; tail-class OOD unreliable</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Unified OOD detection under class imbalance without sacrificing ID classification accuracy</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Class-aware bias term between balanced/imbalanced OOD scores; training-time regularization</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT + OOD sets (SVHN, LSUN, iSUN)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>ODIN, Energy, VOS, LogitAdj, GDFR</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>OOD detection under varying IR; ID classification accuracy retention analysis</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>AUROC, FPR95, AUPR; ID accuracy</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Improves OOD detection especially for tail-class inputs; training-time approach avoids test-time overhead</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>Bias term requires balanced reference distribution; difficult to calibrate for extreme IR</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>NeurIPS 2024</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="6" t="n">
         <v>2024</v>
       </c>
+      <c r="O10" s="6" t="n"/>
     </row>
     <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>PRL</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>PRL: Controllable Long-tail Learning via Preference Representation Learning</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>github.com/DataLab-atom/PRL</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Fixed LT methods can't adapt head-tail trade-off; users need flexible control without retraining</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Enable flexible and continuous head-tail performance trade-off at inference time</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Hypernetwork-generated diverse experts; Dirichlet distribution for preference vectors; expert ensemble at inference</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>LDAM, BalancedSoftmax, MiSLAS, DisAlign, BCL</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>LT classification with varying preference vectors; Pareto frontier analysis</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Accuracy (many/medium/few), balanced accuracy, Pareto frontier coverage</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>Smooth head-tail trade-off via preference sampling; hypernetwork generalizes across preference space</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Hypernetwork adds parameters and training complexity; Dirichlet sampling sensitivity</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>NeurIPS 2024</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="7" t="n">
         <v>2024</v>
       </c>
+      <c r="O11" s="7" t="n"/>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>NCMC</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Neural Collapse To Multiple Centers For Imbalanced Data</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Standard NC collapses minority features to single center; fixed ETF classifiers don't outperform learnable ones</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Design GCR and Cosine Loss to induce Neural Collapse to Multiple Centers (NCMC) for imbalanced learning</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>GCR (Generalized Classification Rule); UFM + MSE-type loss analysis; Cosine Loss for fixed classifiers; class-aware center count strategy</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>CIFAR-10, CIFAR-100</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>LDAM, KCL, ARBLoss, ETF, ARB, standard CE</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>LT classification with fixed vs. learnable classifiers; UFM theoretical analysis</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>Accuracy (head/medium/tail), balanced accuracy</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>NCMC Cosine Loss matches SOTA; multiple centers allow minority features to align across more directions</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>Multiple center count requires heuristic strategy; UFM assumes unconstrained features</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>NeurIPS 2024</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="6" t="n">
         <v>2024</v>
       </c>
+      <c r="O12" s="6" t="n"/>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>LLM-AutoDA</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>LLM-AutoDA: LLM-Driven Automatic Data Augmentation for Long-tailed Problems</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>github.com/DataLab-atom/LLM-LT-AUG</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Manual DA strategies suboptimal and not adaptive; fixed strategies can't respond to training dynamics</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Automate discovery of optimal class-wise DA strategies for long-tail data via LLMs</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>LLM as augmentation strategy generator; val-performance reward signal; iterative strategy refinement; class-wise statistics guide LLM prompts</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT, multiple LT benchmarks</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>AutoAugment, CUDA, DODA, RandAugment, rebalancing baselines</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>LT classification with automated DA search; strategy analysis and ablation</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Accuracy (many/medium/few), overall accuracy</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>LLM-AutoDA outperforms manual DA and rebalancing methods; discovers novel effective strategies</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>LLM API cost and latency; strategies may not generalize cross-dataset; slow iterative refinement</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>NeurIPS 2024</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="7" t="n">
         <v>2024</v>
       </c>
+      <c r="O13" s="7" t="n"/>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>EPIC</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>EPIC: Effective Prompting for Imbalanced-Class Tabular Data Synthesis via LLMs</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>github.com/seharanul17/EPIC (inferred from paper)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>LLMs struggle to generate high-quality minority tabular samples; prompt design unexplored for imbalanced tabular</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Identify effective prompt designs for LLM-based imbalanced tabular data synthesis</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>CSV-style balanced grouped prompting; unique variable mapping (random alphanumeric tokens); class-balanced example grouping in context</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>6 real-world tabular datasets (Travel, Adult, etc.) + toy dataset</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>GReaT, TabDDPM, CTGAN, CopulaGAN, TVAE, CTABGAN</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>Tabular data synthesis quality evaluation + downstream ML classification on imbalanced data</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>Specificity, Sensitivity; downstream classifier accuracy (XGBoost, CatBoost, LightGBM, GBM)</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>EPIC achieves high specificity AND sensitivity simultaneously; outperforms fine-tuned GReaT; model-agnostic</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>Relies on GPT-3.5 API; prompt design may need per-dataset adaptation; slower than direct generative models</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>NeurIPS 2024</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="6" t="n">
         <v>2024</v>
       </c>
+      <c r="O14" s="6" t="n"/>
     </row>
     <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>DiffMatch</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Towards Unbiased Learning in Semi-supervised Semantic Segmentation</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>github.com/yuisuen/DiffMatch</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Discriminative pseudo-label methods suffer Matthew effect: head-class bias degrades tail-class pseudo labels</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Mitigate Matthew effect in semi-supervised segmentation via generative diffusion model perspective</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Semi-sup segmentation as conditional discrete data generation; denoising diffusion process for pseudo-label; debiased adjustment to reverse conditional probability</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Cityscapes, PASCAL VOC (1/16 and 1/4 label protocols)</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>UniMatch, DDFP, RankMatch, U²PL, AEL</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Semi-supervised semantic segmentation under limited label and class imbalance scenarios</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>mIoU (head/tail classes separately), overall mIoU</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>+2.6%/+2.0% over DDFP/RankMatch; head class retained; tail class significantly improved</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Diffusion inference slower than discriminative methods; debiasing calibration sensitive to distribution estimate</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>ICLR 2025</t>
         </is>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O15" s="7" t="n"/>
     </row>
     <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>TTC</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>A Tale of Two Classes: Adapting SupCon to Binary Imbalanced Datasets</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>github.com/aiforvision/TTC</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>SupCon collapses minority embeddings to a single point in binary imbalanced settings; no prior study on this</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Diagnose SupCon failure in binary imbalance; propose new metrics and fixes</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>SAA (Sample Alignment Accuracy) + CAC (Class Alignment Consistency) diagnostic metrics; two new SupCon strategies for binary imbalance</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>7 binary natural and medical imaging datasets (varying IR)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>SupCon, CE, LDAM, BCL, SimCLR</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>Binary classification with increasing IR; representation space analysis via SAA/CAC</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>AUC, balanced accuracy, SAA, CAC</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>SupCon fails progressively with IR increase; proposed fixes boost accuracy up to +35% over SupCon and +5% over SOTA</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>Binary-specific analysis; not validated on multi-class LT settings</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>CVPR 2025</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O16" s="6" t="n"/>
     </row>
     <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>LFN</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Learning from Neighbors: Category Extrapolation for Long-Tail Learning</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>shizhen-zhao.github.io/LT_Neighbors/</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Tail classes lack samples; datasets with finer granularity are less affected by imbalance</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Improve tail representation via open-set auxiliary categories from LLM-driven web crawling</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>LLM-based auxiliary category discovery (fine-grained related classes); automated web image crawling; neighbor-silencing loss; auxiliary classifier masking at inference</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>ImageNet-LT, iNat18; pilot study on ImageNet-21k and OpenImage</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>BalancedSoftmax, RIDE, ResLT, MiSLAS, DINOv2-based baselines</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>LT classification with auxiliary data; granularity vs. imbalance pilot study</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Accuracy (many/medium/few), overall accuracy</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>Category extrapolation consistently improves all class frequencies; finer granularity reliably reduces imbalance gap</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>Web image quality variable; auxiliary data acquisition pipeline is complex and dataset-dependent</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>CVPR 2025</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O17" s="7" t="n"/>
     </row>
     <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>From Head to Tail: Balanced Representation in LVLMs via Adaptive Data Calibration</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>LVLMs trained on long-tail instruction data over-represent head concepts; tail visual concepts underperform</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Mitigate LT problem in LVLM training without increasing data volume</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>3-stage ADR: (1) Analyzing Stage (token/object/co-occurrence/interrogation distributions), (2) Data Rebalancing (filter redundant head), (3) Data Synthesis (DDPM for tail)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>LLaVA training data; 11 VQA/VL benchmarks (MME, POPE, VQAV2, etc.)</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>LLaVA 1.5, ShareGPT4V, ALLaVA, Mini-GPT4V</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>LVLM evaluation on VQA, visual reasoning, hallucination, and tail-concept benchmarks</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>MME score, POPE accuracy, VQA accuracy; tail-30% concept accuracy</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>+4.36% avg over LLaVA 1.5 across 11 benchmarks without adding training data; tail concepts significantly improved</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>Entity-level analysis may miss complex relational imbalances; DDPM tail synthesis quality varies</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>CVPR 2025</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O18" s="6" t="n"/>
     </row>
     <row r="19" ht="72" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>TAET</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>TAET: Two-Stage Adversarial Equalization Training on Long-Tailed Distributions</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>github.com/BuhuiOK/TAET-Two-Stage-Adversarial-Equalization-Training-on-Long-Tailed-Distributions</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Adversarial training on long-tail data fails for tail classes; AT-BSL suffers from robustness overfitting on rare classes</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Achieve balanced adversarial robustness across head and tail classes in long-tail distributions</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Two-stage: CE stabilization phase + HARL (Hierarchical Adversarial Robust Learning); Balanced Robustness metric</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>AT-BSL, TRADES, RoBal, MART, LAS-AT, GAIRAT, HE</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Adversarial training on LT datasets; PGD-20 attack evaluation; robustness-accuracy trade-off analysis</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Balanced Accuracy (clean + adversarial), Balanced Robustness</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>TAET outperforms AT-BSL in balanced accuracy and tail robustness; memory-efficient two-stage design</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Only tested on CIFAR; AT still computationally expensive; two-stage schedule requires tuning</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>CVPR 2025</t>
         </is>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O19" s="7" t="n"/>
     </row>
     <row r="20" ht="72" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>TinyChange</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>A Tiny Change, A Giant Leap: LT Class-Incremental Learning via Geometric Prototype Alignment</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>github.com/laixinyi023/Geometric-Prototype-Alignment</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>LT-CIL suffers gradient competition from head classes and catastrophic forgetting; random classifier init causes misalignment</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Mitigate temporal bias (forgetting) and structural bias (head dominance) in long-tailed class-incremental learning</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>GPA: (1) frozen prototype estimation, (2) geometric weight initialization on unit hypersphere (Fisher criterion), (3) Dynamic Anchoring Optimization</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>CIFAR-100-LT, ImageNet-LT, ImageNet-R</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>LU-CIR, DualPrompt, DER, iCaRL, EASE, RPAC, Gradient Reweighting</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>LT class-incremental learning; plug-and-play ablation with 10 CIL frameworks</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>Avg incremental accuracy, forgetting rate, tail class precision</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>+6.11% avg accuracy, -6.38% forgetting on CIFAR-100-LT; 2.7× convergence acceleration; plug-and-play</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>Prototype quality depends on frozen pretrained features; assumes feature extractor quality sufficient</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>ICCV 2025</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O20" s="6" t="n"/>
     </row>
     <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>MGS</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Long-Tailed Classification with Multi-Granularity Semantics</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Head-to-tail knowledge transfer ignores class differences; fixed label hierarchy misses cross-subtree similarities</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Discover implicit semantic similarities across classes for multi-granularity knowledge transfer in LT recognition</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>LLM-generated multi-level class descriptions; sentence-transformer semantic similarity matrix; multi-granularity semantic knowledge graph; SKCL (semantic knowledge-driven contrastive learning)</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>BCL, TSC, MiSLAS, PaCo, BalancedSoftmax, LLM-AutoDA</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>LT classification; semantic similarity analysis; ablation on granularity levels</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Accuracy (many/medium/few), overall accuracy</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>SKCL improves tail accuracy without compromising head; multi-granularity beats fixed hierarchy</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>LLM descriptions may be noisy; sentence-transformer may miss visual nuance not captured in text</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>ICCV 2025</t>
         </is>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O21" s="7" t="n"/>
     </row>
     <row r="22" ht="72" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>NodeImport</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>NodeImport: Imbalanced Node Classification with Node Importance Assessment</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>github.com/NanChanNN/NodeImport</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>GNNs overfit majority nodes; existing methods treat all minority nodes equally, ignoring intra-class differences and graph structure</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Identify and prioritize valuable training nodes via importance assessment using balanced meta-sets</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Balanced meta-set for importance scoring; tractable importance formula η_v (no extra model needed); framework supports labeled/unlabeled/synthetic nodes; clustering-based meta-set construction</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>3 citation datasets (Cora, Citeseer, etc.), 2 Amazon co-purchase datasets</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>GCN, GAT, GraphSAGE + oversampling/reweighting (GraphSMOTE, ImGAGN, TAM)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Node classification on imbalanced graphs; importance formula ablation; varying IR study</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>Macro-F1, balanced accuracy, per-class F1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>NodeImport outperforms SOTA; importance formula naturally provides filtering threshold; adaptable to any node generator</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>Meta-set quality sensitive to extreme class imbalance; bi-level approximation loses some precision</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>KDD 2025</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O22" s="6" t="n"/>
     </row>
     <row r="23" ht="72" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>ORD</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Synthetic Tabular Data Generation for Imbalanced Classification: Effectiveness of an Overlap Class</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>github.com/Annie2603/ORD</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Deep generative models produce lower-quality minority samples in imbalanced settings; overlap region degrades generation</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Improve generative model quality for minority class by identifying and handling the majority-minority overlap region</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>ORD (Overlap Region Detection): k-fold CV random forest to identify overlapping majority instances → ternary labeling (minority/overlap/clear majority) → conditional generation → train classifier excluding overlap</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>4 real-life tabular datasets; 5 generative models (CTGAN, TabDDPM, ForestFlow, TabSyn, GReaT); 5 classifiers</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>SMOTE, CTGAN, TabDDPM, ForestFlow, TabSyn baseline (without ORD)</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Imbalanced binary tabular classification with synthetic augmentation; ablation on each ORD component</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Specificity, Sensitivity, overall accuracy; Oracle Bayesian accuracy</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>ORD improves both generator quality and classifier accuracy; compatible with all tested generators</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>k-fold CV adds training overhead; designed for binary imbalance; threshold τ requires tuning</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>AAAI 2025</t>
         </is>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="7" t="n">
         <v>2025</v>
       </c>
+      <c r="O23" s="7" t="n"/>
     </row>
     <row r="24" ht="72" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>DBM</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Difficulty-aware Balancing Margin Loss for Long-tailed Recognition</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>github.com/quotation2520/dbm_ltr</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Class-level rebalancing ignores instance-level difficulty; hard samples within classes under-addressed</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Jointly address class imbalance and instance difficulty via a dual-component margin loss</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>DBM loss = class-wise margin (∝ class frequency) + instance-wise margin (angular distance to class center for hard positives)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT, iNaturalist2018</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>LDAM, BalancedSoftmax, BCL, MiSLAS, PaCo, LogitAdj</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>LT image classification; ablation on class-wise vs. instance-wise margins; plug-in with existing methods</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>Accuracy (many/medium/few), overall accuracy</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>DBM consistently improves when combined with existing LT methods; instance-wise margin crucial for hard positive samples</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>Angular distance per sample adds overhead; two margin components require careful tuning</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>AAAI 2025</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="N24" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="O24" s="6" t="n"/>
     </row>
     <row r="25" ht="72" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>BCE3S</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>BCE3S: Binary Cross-Entropy Based Tripartite Synergistic Learning for Long-tailed Recognition</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>github.com/wakinghours-github/BCE3S</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>CE-Softmax couples imbalanced classifier vectors amplifying imbalance; BCE decouples metrics but TSL with BCE unexplored</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Design BCE-based tripartite synergistic learning integrating joint learning, contrastive learning, and uniform classifier learning</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>BCE3S = L_sc_bce (joint feature-classifier BCE) + L_ss_bce (BCE-based contrastive) + L_cc_bce (BCE-based uniform classifier separability)</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT, iNaturalist2018</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>CB Loss, RIDE, BCL, DisCo, ETF, RBL, NC-cRT</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>LT classification at various IF; ablation on each BCE component; comparison to all three TSL modes</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Accuracy (many/medium/few), overall accuracy</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>SOTA 59.50% on CIFAR-100-LT IF=100; BCE uniform learning effectively balances classifier separability</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>BCE-based training more complex than CE; three-component loss requires careful tuning of relative weights</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>AAAI 2026 (arXiv Nov 2025)</t>
         </is>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="7" t="n">
         <v>2026</v>
+      </c>
+      <c r="O25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="72" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Rethinking Classifier Re-Training in Long-Tailed Recognition: Label Over-Smooth Can Balance</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Thinklab-SJTU/LOS</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Classifier re-training (Stage 2 of decoupled training) still fails on LT data because logit magnitudes vary wildly across classes; no diagnostic metric existed</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Introduce Logits Magnitude (LoMa) metric to diagnose logit imbalance; propose Label Over-Smoothing (LOS) to prevent over-concentration of logits toward head classes</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Label Over-Smoothing: softens one-hot labels (true class slightly above 1/K, others slightly below); does not require class-frequency priors; plug-and-play into any decoupled framework</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CIFAR-100-LT, ImageNet-LT, iNaturalist 2018</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>LA, cRT, MiSLAS, GCL, PaCo, BCL, RIDE</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Long-tailed multi-class image classification at multiple imbalance ratios; many/medium/few-shot split analysis</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Top-1 accuracy (overall, many, medium, few splits)</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>LOS consistently outperforms all baselines on all three benchmarks; does not require knowledge of class frequencies at training time; compatible with existing Stage-1 methods</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Only addresses classifier re-training (Stage 2); does not improve representation quality from Stage 1</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>ICLR 2025</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>https://openreview.net/pdf?id=OeKp3AdiVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>ConMix</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>ConMix: Contrastive Mixup at Representation Level for Long-tailed Deep Clustering</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/LZX-001/ConMix</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Deep clustering assumes balanced cluster distributions; real data is long-tailed but almost no prior work addresses long-tailed deep clustering</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Design a contrastive clustering method that explicitly handles long-tailed class distributions without class-count labels</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Mixup at the representation level within a contrastive learning framework; theoretical proof that mixup-augmented contrastive objective re-balances gradient contributions across classes</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT (multiple imbalance ratios)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>SCAN, SPICE, GCC and other deep clustering baselines</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Unsupervised clustering under long-tail distribution; evaluated across multiple IR values</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Accuracy (ACC), Normalized Mutual Information (NMI), Adjusted Rand Index (ARI)</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>ConMix outperforms all state-of-the-art deep clustering methods across multiple imbalance ratios; representation-level mixup more effective than input-level mixup for clustering</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Evaluated primarily on visual data; real-world tabular or text clustering not explored</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>ICLR 2025</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>https://openreview.net/pdf?id=3lH8WT0fhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>LTRL</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>LTRL: Boosting Long-Tail Recognition via Reflective Learning</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/fistyee/LTRL</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Long-tail recognition faces three intertwined problems: biased predictions on old samples, unrecognized cross-class feature relationships, and gradient conflicts between competing losses; prior work addresses each separately</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Design a unified plug-and-play module that simultaneously corrects bias, enriches cross-class features, and harmonizes loss gradients</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Three lightweight modules: (1) reflection buffer reviewing past biased predictions; (2) cross-class feature relation summarization; (3) gradient conflict correction to harmonize multi-loss training</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CIFAR-10/100-LT (ResNet-32), ImageNet-LT (ResNeXt-50), Places-LT (ResNet-152), iNaturalist 2018 (ResNet-50)</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>LDAM, BBN, MiSLAS, PaCo, GCL, TSC, SBCL</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Plug-in evaluation on top of existing LT methods; ablation of each module contribution</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Top-1 accuracy (overall, many, medium, few splits)</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>LTRL consistently improves all plugged-in baselines; gradient conflict correction alone yields significant gains on tail classes</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Adds memory overhead for reflection buffer; evaluated only on standard vision benchmarks</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>ECCV 2024</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2407.12568</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>DaSC</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Distribution-Aware Robust Learning from Long-Tailed Data with Noisy Labels</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/JaesoonBaik1213/DaSC</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Real-world data is simultaneously long-tailed AND noisy; standard sample selection methods estimate class centroids from high-confidence samples and fail for tail classes that have too few clean examples</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Jointly handle long-tail imbalance and label noise via distribution-aware centroid estimation and balanced contrastive learning</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Distribution-aware Class Centroid Estimation (DaCC): confidence-weighted centroid over all samples; Semi-supervised Balanced Contrastive Loss (SBCL) for clean samples; Mixup Instance Discrimination Loss (MIDL) for noisy samples</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>CIFAR-10-LT + noise, CIFAR-100-LT + noise, mini-ImageNet-LT + noise (IR=100)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>DivideMix, Sel-CL, DISC, RoLT</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Simultaneous LT + noisy-label settings at varying noise rates and imbalance ratios</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Top-1 accuracy (overall, many/medium/few splits)</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>DaCC-based centroid estimation significantly improves tail-class centroid quality; outperforms all LT+noisy baselines consistently</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Two-stage pipeline; requires clean validation set for threshold tuning</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>ECCV 2024</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2407.16802</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>RRB</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Rectify the Regression Bias in Long-Tailed Object Detection</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>LT detection research focused exclusively on classification bias; the regression branch also suffers from imbalance—head-class samples dominate regression training, causing poor localization on tail classes</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Identify and correct regression-level bias in long-tailed object detection independently of classification-level bias correction</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Three complementary solutions: (1) class-agnostic regression branch training on all classes; (2) clustering regression heads for visually similar classes; (3) merged regression heads for rare classes sharing parameters across similar classes</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>LVIS v1.0 (long-tailed instance segmentation and detection benchmark)</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Mask-RCNN, EQL, BAGS, SEESAW, LO-DET</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Long-tailed object detection and instance segmentation; analysis of regression vs. classification bias</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>AP, AP_r (rare), AP_c (common), AP_f (frequent) on LVIS</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Regression bias is a distinct and significant source of tail-class degradation; combining regression and classification bias corrections yields additive improvement</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>Extra inference overhead from class-agnostic branch; evaluated only on LVIS</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>ECCV 2024</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2401.15885</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>SIMBA</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Graph Size-imbalanced Learning with Energy-guided Structural Smoothing</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Graph classification datasets follow power-law distributions of graph sizes; GNNs overfit large (head) graphs and underperform on small (tail) graphs, a problem distinct from class imbalance</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Correct size-imbalanced learning in graph classification by energy-guided structural smoothing between head and tail graphs</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Graphs-to-Graph abstraction using inter-graph correlations; energy-based message-passing belief propagation re-weighting under-represented (small) graphs during training; structural feature smoothing across graph sizes</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>REDDIT-B, IMDB-B, MUTAG, PROTEINS, COLLAB</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>GK, WL, GIN, DIFFPOOL, SOLT-GNN</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Graph classification under size-imbalanced distributions; ablation of smoothing components</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Accuracy, Macro-F1</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>SIMBA achieves 82.70% accuracy and 81.28% Macro-F1 on REDDIT-B vs. SOLT-GNN's 77.20%/80.43%; energy-guided smoothing effectively transfers head-graph information to size-tail graphs</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Graphs-to-Graph construction adds computational overhead; evaluated on small academic graph datasets</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>WSDM 2025</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2412.17591</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>AD-GSMOTE</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Enhancement for Imbalanced Multi-relation Graph Learning</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/graphprojects/AD-GSMOTE</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Multi-relation graphs suffer from class imbalance; existing graph oversampling methods ignore multi-relational structure and degree heterogeneity of minority-class nodes</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Adapt SMOTE for multi-relation graphs by generating structurally valid and semantically meaningful minority synthetic nodes</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Degree-filtered minority node selection; adaptive center-node generator using correctly classified nodes; triadic edge generator for synthetic connectivity; semantic attention for multi-relation fusion; class-aware logit calibration at inference</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Twitter-Drug, YelpChi, Amazon</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>GraphSMOTE, ImGAGN, GraphMixup, PC-GNN, RawlsGCN</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Node classification under class imbalance on multi-relation graphs; ablation of each component</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Macro-F1, AUC</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>AD-GSMOTE achieves best Macro-F1 on all three datasets; adaptive center-node generation critical for synthetic quality</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>Degree-filter heuristic may fail if minority classes are not degree-sparse; Twitter-Drug is a proprietary dataset</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>WSDM 2025</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/doi/10.1145/3701551.3703553</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>MATI</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Adapting to Evolving Data: Test-Time Expert Aggregation for Imbalanced Tabular Regression</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Imbalanced regression on tabular data is worsened when test distributions shift over time; existing imbalanced regression methods fail under test-time distribution shift</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Handle imbalanced tabular regression with test-time distribution shift via a mixture-of-experts approach requiring no retraining</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>GMM-identified data sub-populations; specialized experts trained per region on synthetically augmented data; self-supervised test-time aggregation dynamically re-weights experts based on incoming test features</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>House pricing, bike sharing, age prediction, and one additional tabular regression dataset</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>SMOGN, ReSample, REBAGG, DIR</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Imbalanced tabular regression under distributional shift; comparison of static vs. adaptive expert aggregation</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>MAE, RMSE (focus on rare-value prediction)</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>MATI achieves 7.1% average MAE improvement over best baseline; gains are larger under distribution shift conditions</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Short paper (4 pages); GMM component count is a manual hyperparameter; no theoretical guarantee on adaptation quality</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>WSDM 2026</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2506.07033</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>GraphMuGu</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Generate or Re-Weight? A Mutual-Guidance Method for Class-Imbalanced Graphs</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Node classification with class imbalance is addressed via generation or re-weighting in isolation; each strategy has blind spots the other can correct</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Unify generative oversampling and sample re-weighting in a mutual-guidance framework where each branch informs the other</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Generative branch produces synthetic minority nodes guided by re-weighting branch confidence; re-weighting branch adjusts importance using generation quality signals; uncertainty-aware synthesis-quantity estimator; similarity-aware sample weighting</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Five class-imbalanced graph datasets (long-tailed and step-imbalance settings)</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>GraphSMOTE, DPGNN, ImGAGN, GraphMixup, TAM, LTE4G</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Node classification under both long-tailed and step-imbalanced distributions</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Macro-F1, AUC</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>GraphMuGu outperforms all baselines on both imbalance settings; mutual guidance significantly outperforms using either branch alone</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Joint training complexity; mutual guidance may be unstable if one branch diverges early</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>IJCAI 2025</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ijcai.org/proceedings/2025/0409.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>DILDL</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Decoupled Imbalanced Label Distribution Learning</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>In Label Distribution Learning (LDL), dominant labels receive far higher description degrees than non-dominant labels, causing the model to ignore non-dominant label information during training</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Decouple the label distribution into dominant and non-dominant components and independently balance their gradient contributions</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Decomposition of label distributions into dominant and non-dominant parts; separate Gaussian distribution alignment for each component; decoupled representation learning to independently calibrate imbalanced description degrees</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Standard LDL benchmarks (expression analysis, age estimation)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>SA-BFGS, LDLSF, LDLM, IncomLDL</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Multi-label soft distribution learning under dominant-label bias; ablation of decoupled components</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Clark distance, Chebyshev distance, Canberra metric, KL divergence</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>DILDL outperforms all LDL baselines; decoupled treatment of dominant vs. non-dominant labels is key to the improvement</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Focused on soft label distribution scenarios; not directly applicable to hard multi-class classification</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>IJCAI 2025</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.ijcai.org/proceedings/2025/0579.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>LT-SpikeFormer</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Tackling Long-Tailed Data Challenges in Spiking Neural Networks via Heterogeneous Knowledge Distillation</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Spiking Neural Networks are energy-efficient but completely unexplored for long-tailed recognition; binary spike representations make SNNs more vulnerable to class imbalance than ANNs</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Enable long-tailed recognition in SNNs by transferring rich multi-scale representations from a pre-trained ANN teacher via heterogeneous knowledge distillation</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Transformer-based SNN architecture; heterogeneous knowledge distillation from ANN teacher; hierarchical cross-layer feature distillation transferring multi-scale representations to compensate for SNN's limited tail-class capacity</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT (IR=10, 50, 100)</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>BKD (SNN baseline), MDCS (self-distillation SNN), standard ANN LT methods</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Long-tailed recognition in SNN vs. ANN settings; analysis of spike-rate distribution across classes</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Top-1 accuracy (overall, many, medium, few splits)</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>LT-SpikeFormer improves 5–10% over BKD (SNN baseline); heterogeneous distillation more effective than homogeneous SNN self-distillation</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Requires large ANN teacher at training time; real-world neuromorphic chip deployment not tested</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>IJCAI 2025</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ijcai.org/proceedings/2025/0157.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>CFAMG</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Mitigating Data Imbalance in Time Series Classification Based on Counterfactual Minority Samples Augmentation</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Temporal dependencies make naive oversampling (SMOTE) fail for imbalanced time series—it ignores temporal structure and generates unrealistic interpolations</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Generate realistic counterfactual minority time-series samples via causal disentanglement to address class imbalance</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Disentangled encoder separating causal (class-determining) and non-causal (style) factors; counterfactual intervention replacing minority causal factors; mutual information constraints for disentanglement; minority class decoder for realistic synthesis</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>53 constructed imbalanced datasets from UCR/UEA time-series benchmarks</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>SMOTE, ADASYN, TimeGAN, TSMOTE and other temporal oversampling methods</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Imbalanced time-series classification across 53 datasets; classifier comparison (MLP, LSTM, ResNet)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>Macro-F1, AUC (focus on minority class performance)</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>CFAMG improves 24.0%/18.6%/6.6% over best non-temporal method and 26.0%/22.2%/9.5% over best temporal method across three classifiers</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Causal factor disentanglement is approximate; sensitive to encoder architecture choice</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>KDD 2025</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/doi/10.1145/3711896.3737049</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>OVO-OVR</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Revisiting One-Versus-One and One-Versus-Rest: Insights into Imbalanced Multi-class Classification</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>OVO and OVR decomposition strategies are affected differently by class imbalance, but no systematic analysis exists; practitioners default to OVR without theoretical justification</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Theoretically and empirically analyze when OVO vs. OVR is preferable under imbalanced multi-class settings; provide actionable guidelines</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Analytical conditions for OVO/OVR preference under varying imbalance ratios; theoretical bounds on error propagation under decomposition; empirical verification across classifiers and datasets</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Standard imbalanced multi-class benchmarks from UCI/LIBSVM</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>SVM and gradient boosting under OVO vs. OVR decomposition</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Systematic comparison of OVO/OVR across classifiers, imbalance ratios, and number of classes</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Macro-F1, Balanced Accuracy, G-mean</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>OVO consistently outperforms OVR under severe imbalance conditions; head classes in OVR negatively affect tail-class binary classifiers</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Primarily focused on linear/kernel classifiers; implications for deep neural networks remain unclear</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>ICDM 2025</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>https://www3.cs.stonybrook.edu/~icdm2025/acceptedpapers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Uni-GNN</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Overcoming Class Imbalance: Unified GNN Learning with Structural and Semantic Connectivity Representations</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Class-imbalanced node classification is exacerbated by GNNs' reliance on 1-hop neighborhood aggregation, which limits information diffusion for isolated minority-class nodes</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Unify structural and semantic connectivity in GNNs with balanced pseudo-label generation to leverage unlabeled nodes for minority class augmentation</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Dual structural+semantic connectivity representation; information diffusion beyond 1-hop neighbors for minority-class nodes; balanced pseudo-label generation from unlabeled nodes; joint self-training objective</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Standard node classification benchmarks (Cora, Citeseer, Amazon) with induced class imbalance</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>GraphSMOTE, DPGNN, ImGAGN, TAM, LTE4G</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Node classification under class imbalance; analysis of 1-hop vs. extended connectivity</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>Macro-F1, AUC</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Extending connectivity beyond 1-hop significantly benefits minority-class nodes; unified structural+semantic representation outperforms each modality alone</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Pseudo-label quality degrades under severe imbalance; extended connectivity increases computational cost</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>NeurIPS 2025</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>https://neurips.cc/virtual/2025/poster/127625</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>IP-DPP</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Long-Tailed Recognition via Information-Preservable Two-Stage Learning</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/fudong03/BNS_IPDPP</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Two-stage decoupled training can lose valuable tail-class information in Stage 2 by naive balanced sampling, which discards head-class data</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Rectify majority bias in classifier re-training while preserving maximum information from all classes including head classes</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1: Balanced Neighborhood Sampling (BNS) minimizing intra-class feature distance; Stage 2: Information-Preservable Determinantal Point Process (IP-DPP) selecting maximally diverse, informative data subsets that naturally balance classes</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT, iNaturalist 2018</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>KCL, TSC, SBCL, MiSLAS, BCL</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Two-stage LT recognition; ablation of BNS and IP-DPP contributions; comparison of sampling strategies</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Top-1 accuracy (overall, many, medium, few splits)</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>IP-DPP achieves state-of-the-art across all benchmarks; preserving head-class diversity in Stage 2 is critical for overall accuracy</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>DPP inference has cubic complexity in set size; approximation methods needed for large datasets</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>NeurIPS 2025</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2510.08836</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>IBCL</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Improved Balanced Classification with Theoretically Grounded Loss Functions</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Logit-Adjusted (LA) and class-weighted losses are dominant but lack strong theoretical backing; H-consistency bounds are needed to identify theoretically sound loss families</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Derive H-consistency bounds for balanced classification losses and propose improved loss families (GLA and GCA) with stronger theoretical guarantees</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Generalized Logit-Adjusted (GLA) losses extending LA to full cross-entropy family; Generalized Class-Aware weighted (GCA) losses with class-dependent confidence margins; GCA achieves H-consistency bound scaling as 1/√p_min under severe imbalance</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>CIFAR-LT, ImageNet-LT (standard imbalanced classification benchmarks)</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Standard CE, LA loss, class-weighted CE</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Balanced multi-class classification under varying imbalance ratios; theoretical analysis of bounds</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>Balanced accuracy, Macro-F1</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>GCA achieves the strongest theoretical guarantees under severe imbalance (1/√p_min scaling); GLA outperforms LA on common benchmarks</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>Empirical gains over LA are modest; theoretical results assume specific hypothesis class conditions</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>NeurIPS 2025</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2512.23947</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>OSB-SMOTE</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Concentration and excess risk bounds for imbalanced classification with synthetic oversampling</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>SMOTE is widely used for imbalanced classification but lacks theoretical justification; no concentration or excess risk guarantees exist for classifiers trained on SMOTE-generated data</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Provide the first rigorous theoretical framework for SMOTE including concentration bounds, excess risk guarantees, and parameter guidance</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Uniform concentration bound on empirical risk over synthetic minority samples; nonparametric excess risk guarantee for kernel classifiers trained with synthetic oversampling; optimal parameter guidance for k-neighbors and mixing coefficients</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Standard imbalanced classification datasets (theoretical validation)</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Naive oversampling, no oversampling</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Theoretical derivation with empirical validation on standard imbalanced datasets</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>AUC, Balanced accuracy (empirical); concentration and excess risk bounds (theoretical)</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>First concentration and excess risk bounds for SMOTE; optimal SMOTE parameter regime identified; kernel classifier trained on SMOTE data converges at optimal nonparametric rate</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Results restricted to kernel classifiers; neural network extensions remain open</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>NeurIPS 2025</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2510.20472</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>ImGDA</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Dual Prototype-Enhanced Contrastive Framework for Class-Imbalanced Graph Domain Adaptation</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/maxin88scu/ImGDA</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Graph domain adaptation fails when source domain has class imbalance—standard alignment incorrectly aligns rare source classes to head target classes</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Correct source-domain class imbalance during cross-graph domain adaptation via dual-prototype contrastive learning</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Dual-branch graph encoder (local + global) generating class-specific prototypes; cross-branch contrastive learning within source domain to mitigate imbalance; cross-domain contrast with pseudo-labels to align semantically similar cross-domain pairs</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Standard graph domain adaptation benchmarks (Citation network variants)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>DANN, CDAN, UDAGCN, JHGDA and other graph domain adaptation methods</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Unsupervised graph domain adaptation under class-imbalanced source domains; ablation of local vs. global prototype contributions</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>Macro-F1, Node classification accuracy</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>ImGDA outperforms all graph domain adaptation baselines; dual-branch prototype generation critical for cross-domain class alignment</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>Requires selecting anchor prototypes (sensitive to anchor quality); limited to unsupervised target settings</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>NeurIPS 2025</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>https://openreview.net/pdf?id=QSK8VqiijI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="72" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>RLAL</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Revisiting Long-Tailed Learning: Insights from an Architectural Perspective</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>All existing LT methods treat network architecture as fixed and only modify training procedures; the architecture itself may introduce imbalance bias</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Analyze how topology, convolution type, and activations affect LT performance; design LT-aware architectures via Neural Architecture Search</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>LT-AggConv and LT-HierConv novel operations for LT robustness; LT-DARTS NAS with long-tail-aware search space and unbiased search strategy; discovered architectures combinable with existing loss/sampling methods</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CIFAR-10-LT, CIFAR-100-LT, ImageNet-LT</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Standard ResNet, ResNeXt; LA loss, MiSLAS as combined baselines</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Architecture search for LT; ablation of LT-AggConv/LT-HierConv; combination with existing LT training methods</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Top-1 accuracy (overall, many, medium, few splits)</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Architectural design is an independent and additive source of LT improvement; LT-DARTS architectures stack with method-level gains</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>NAS search is computationally expensive; discovered architectures may not generalize across all imbalance ratios</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>CIKM 2025</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2411.06098</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="72" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>GraphIAM</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>GraphIAM: Two-Stage Algorithm for Improving Class-Imbalanced Node Classification on Attribute-Missing Graphs</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Node classification on attribute-missing graphs is doubly hard: missing attributes degrade feature quality, and class imbalance biases training toward majority classes; minority nodes tend to be both attribute-sparse and degree-sparse</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Handle simultaneous attribute incompleteness and class imbalance in node classification via a two-stage algorithm</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Stage 1: attribute imputation using neighborhood aggregation and semantic propagation; Stage 2: imbalance-aware node classification on the completed graph; stages mutually informed to prevent error propagation</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Cora, Citeseer, and other node classification datasets with induced attribute-missing and class-imbalance conditions</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>GraphSMOTE, DPGNN, TAM and attribute-imputation baselines</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Node classification under combined attribute-missing and class-imbalanced conditions</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>Macro-F1, AUC</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>GraphIAM outperforms all baselines; joint consideration of attribute-missingness and imbalance is more effective than addressing each separately</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>Two-stage pipeline: if Stage 1 imputation is poor, Stage 2 cannot recover; evaluated primarily on citation networks</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>CIKM 2025</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cikm2025.org/program/accepted-papers</t>
+        </is>
       </c>
     </row>
   </sheetData>
